--- a/panchang-data/Badrinath2026.xlsx
+++ b/panchang-data/Badrinath2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5395">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16210,6 +16210,9 @@
   </si>
   <si>
     <t>121°05'03.43</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16699,7 +16702,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16785,7 +16788,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16871,7 +16874,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16957,7 +16960,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17043,7 +17046,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17129,7 +17132,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17215,7 +17218,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17301,7 +17304,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17387,7 +17390,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17473,7 +17476,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17559,7 +17562,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17645,7 +17648,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17731,7 +17734,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17817,7 +17820,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17903,7 +17906,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17989,7 +17992,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18075,7 +18078,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18161,7 +18164,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18247,7 +18250,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18333,7 +18336,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18419,7 +18422,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18505,7 +18508,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18591,7 +18594,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18677,7 +18680,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18763,7 +18766,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18849,7 +18852,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18935,7 +18938,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19021,7 +19024,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19107,7 +19110,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19193,7 +19196,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19279,7 +19282,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19365,7 +19368,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19451,7 +19454,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19537,7 +19540,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19623,7 +19626,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19709,7 +19712,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19795,7 +19798,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19881,7 +19884,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19967,7 +19970,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20053,7 +20056,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20139,7 +20142,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20225,7 +20228,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20311,7 +20314,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20397,7 +20400,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20483,7 +20486,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20569,7 +20572,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20655,7 +20658,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20741,7 +20744,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20827,7 +20830,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20913,7 +20916,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20999,7 +21002,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21085,7 +21088,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21171,7 +21174,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21257,7 +21260,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21343,7 +21346,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21429,7 +21432,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21515,7 +21518,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21601,7 +21604,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21687,7 +21690,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21773,7 +21776,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21859,7 +21862,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21945,7 +21948,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>559</v>
+        <v>1001</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22031,7 +22034,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22117,7 +22120,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22203,7 +22206,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22289,7 +22292,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22375,7 +22378,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22461,7 +22464,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22547,7 +22550,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22633,7 +22636,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22719,7 +22722,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22805,7 +22808,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22891,7 +22894,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22977,7 +22980,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23063,7 +23066,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23149,7 +23152,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23235,7 +23238,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23321,7 +23324,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23407,7 +23410,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23493,7 +23496,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23579,7 +23582,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23665,7 +23668,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23751,7 +23754,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23837,7 +23840,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23923,7 +23926,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24009,7 +24012,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24095,7 +24098,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24181,7 +24184,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24267,7 +24270,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24353,7 +24356,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24439,7 +24442,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24525,7 +24528,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24611,7 +24614,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24697,7 +24700,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24783,7 +24786,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24869,7 +24872,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24955,7 +24958,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25041,7 +25044,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25127,7 +25130,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25213,7 +25216,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25299,7 +25302,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25385,7 +25388,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25471,7 +25474,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25557,7 +25560,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25643,7 +25646,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25729,7 +25732,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25815,7 +25818,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25901,7 +25904,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25987,7 +25990,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26073,7 +26076,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26159,7 +26162,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26245,7 +26248,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26331,7 +26334,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26417,7 +26420,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26503,7 +26506,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26589,7 +26592,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26675,7 +26678,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26761,7 +26764,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26847,7 +26850,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26933,7 +26936,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27019,7 +27022,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1442</v>
+        <v>1865</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27105,7 +27108,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27191,7 +27194,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27277,7 +27280,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27363,7 +27366,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27449,7 +27452,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27535,7 +27538,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27621,7 +27624,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27707,7 +27710,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27793,7 +27796,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27879,7 +27882,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27965,7 +27968,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28051,7 +28054,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28137,7 +28140,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28223,7 +28226,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28309,7 +28312,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1865</v>
+        <v>2301</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28395,7 +28398,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28481,7 +28484,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28567,7 +28570,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28653,7 +28656,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28739,7 +28742,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28825,7 +28828,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28911,7 +28914,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28997,7 +29000,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29083,7 +29086,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29169,7 +29172,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29255,7 +29258,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29341,7 +29344,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29427,7 +29430,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29513,7 +29516,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29599,7 +29602,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1865</v>
+        <v>5394</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29685,7 +29688,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29771,7 +29774,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29857,7 +29860,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29943,7 +29946,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30029,7 +30032,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30115,7 +30118,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30201,7 +30204,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30287,7 +30290,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30373,7 +30376,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30459,7 +30462,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30545,7 +30548,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30631,7 +30634,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30717,7 +30720,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30803,7 +30806,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30889,7 +30892,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2301</v>
+        <v>5394</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
